--- a/StructureDefinition-emcare-device.xlsx
+++ b/StructureDefinition-emcare-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-01-10T12:56:19+00:00</t>
+    <t>2022-01-18T13:14:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
